--- a/data/trans_orig/P1418-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2007</t>
+          <t>Población con diagnóstico de mala circulación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73768</t>
+          <t>75749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77477</t>
+          <t>78506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117377</t>
+          <t>116182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>644089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667636</t>
+          <t>667452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614583</t>
+          <t>612602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641972</t>
+          <t>642497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1264986</t>
+          <t>1266181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304886</t>
+          <t>1303857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77033</t>
+          <t>75244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116072</t>
+          <t>112277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124468</t>
+          <t>126297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171147</t>
+          <t>170850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890834</t>
+          <t>891517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>920544</t>
+          <t>920740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>852321</t>
+          <t>856116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>891360</t>
+          <t>893149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1759046</t>
+          <t>1759343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1805725</t>
+          <t>1803896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>62403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96608</t>
+          <t>95553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94387</t>
+          <t>92663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135377</t>
+          <t>132520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631349</t>
+          <t>629209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653491</t>
+          <t>653351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>587233</t>
+          <t>588288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621433</t>
+          <t>621438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226973</t>
+          <t>1229830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267963</t>
+          <t>1269687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68895</t>
+          <t>66372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93573</t>
+          <t>94191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>136114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143192</t>
+          <t>142156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194190</t>
+          <t>191085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873327</t>
+          <t>875850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>901807</t>
+          <t>902386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904425</t>
+          <t>902498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945039</t>
+          <t>944421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1786644</t>
+          <t>1789749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837642</t>
+          <t>1838678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156679</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312259</t>
+          <t>308880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>382390</t>
+          <t>381226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>477027</t>
+          <t>482505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>568283</t>
+          <t>564282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3067846</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3119864</t>
+          <t>3122342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2996807</t>
+          <t>2997971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3066938</t>
+          <t>3070317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6087458</t>
+          <t>6091459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6178714</t>
+          <t>6173236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2012</t>
+          <t>Población con diagnóstico de mala circulación en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54330</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85889</t>
+          <t>87753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73256</t>
+          <t>74530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110185</t>
+          <t>114026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671544</t>
+          <t>671061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689915</t>
+          <t>690326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611161</t>
+          <t>609297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642720</t>
+          <t>643361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1290334</t>
+          <t>1286493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327263</t>
+          <t>1325989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>50626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84853</t>
+          <t>86086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125235</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122536</t>
+          <t>120126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168488</t>
+          <t>167173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966354</t>
+          <t>967321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991587</t>
+          <t>992050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>903738</t>
+          <t>901631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>944120</t>
+          <t>942887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1878433</t>
+          <t>1879748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1924385</t>
+          <t>1926795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37097</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>76831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104271</t>
+          <t>105281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>720526</t>
+          <t>719809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>743029</t>
+          <t>742983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>700587</t>
+          <t>700343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>731286</t>
+          <t>730574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1430526</t>
+          <t>1429516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1469238</t>
+          <t>1468644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>90955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130767</t>
+          <t>131217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>114518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157546</t>
+          <t>159817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912016</t>
+          <t>911273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931950</t>
+          <t>932314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>920088</t>
+          <t>919638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959660</t>
+          <t>959900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841048</t>
+          <t>1838777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886722</t>
+          <t>1884076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>128787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311242</t>
+          <t>309986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>384600</t>
+          <t>383820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409172</t>
+          <t>413206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>496939</t>
+          <t>494468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3295802</t>
+          <t>3297992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3339412</t>
+          <t>3338588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3169452</t>
+          <t>3170232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3242810</t>
+          <t>3244066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6483892</t>
+          <t>6486363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6571659</t>
+          <t>6567625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2016</t>
+          <t>Población con diagnóstico de mala circulación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>33051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67854</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60646</t>
+          <t>60295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94764</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640319</t>
+          <t>641749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659791</t>
+          <t>659708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>604985</t>
+          <t>606362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633156</t>
+          <t>633941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1252875</t>
+          <t>1254193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286993</t>
+          <t>1287344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>50824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>83337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109202</t>
+          <t>110060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>986291</t>
+          <t>986687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006262</t>
+          <t>1006154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>959699</t>
+          <t>959576</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>993175</t>
+          <t>992089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1956142</t>
+          <t>1955284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1992770</t>
+          <t>1992188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>76940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58949</t>
+          <t>59195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98215</t>
+          <t>98952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>732547</t>
+          <t>732336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749293</t>
+          <t>749302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>707081</t>
+          <t>708071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740773</t>
+          <t>741017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1446348</t>
+          <t>1445611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1485614</t>
+          <t>1485368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58856</t>
+          <t>59621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95958</t>
+          <t>98270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73922</t>
+          <t>74809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911477</t>
+          <t>910548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928648</t>
+          <t>927328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947821</t>
+          <t>945509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984923</t>
+          <t>984158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867607</t>
+          <t>1867708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907424</t>
+          <t>1906537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>64345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104793</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222347</t>
+          <t>223146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286891</t>
+          <t>289290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>298226</t>
+          <t>301375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>372207</t>
+          <t>373029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3289557</t>
+          <t>3294473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3328607</t>
+          <t>3330005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3257651</t>
+          <t>3255252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3322195</t>
+          <t>3321396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6566685</t>
+          <t>6565863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6640666</t>
+          <t>6637517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2023</t>
+          <t>Población con diagnóstico de mala circulación en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40420</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>54359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>74673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80627</t>
+          <t>80243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109994</t>
+          <t>109060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595021</t>
+          <t>593506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614333</t>
+          <t>613216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600657</t>
+          <t>600397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>621252</t>
+          <t>620711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1200517</t>
+          <t>1201451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1229884</t>
+          <t>1230268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69087</t>
+          <t>69654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95643</t>
+          <t>94835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77042</t>
+          <t>77495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139779</t>
+          <t>139685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1140021</t>
+          <t>1139398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1172451</t>
+          <t>1172638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>859813</t>
+          <t>860621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>886369</t>
+          <t>885802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007220</t>
+          <t>2007314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2069957</t>
+          <t>2069504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>44746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81830</t>
+          <t>82273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58576</t>
+          <t>57951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111924</t>
+          <t>111680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658631</t>
+          <t>657075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679719</t>
+          <t>678782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>849849</t>
+          <t>849406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>901312</t>
+          <t>901150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521576</t>
+          <t>1521820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1574924</t>
+          <t>1575549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57651</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77927</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119315</t>
+          <t>121644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117407</t>
+          <t>118904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167255</t>
+          <t>166703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868124</t>
+          <t>867925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895072</t>
+          <t>894851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971139</t>
+          <t>968810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1012527</t>
+          <t>1011804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848974</t>
+          <t>1849526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898822</t>
+          <t>1897325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>109528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162460</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246863</t>
+          <t>251747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339833</t>
+          <t>340066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>379743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>493400</t>
+          <t>483252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3292120</t>
+          <t>3291289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3345875</t>
+          <t>3345052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3312826</t>
+          <t>3312593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3405796</t>
+          <t>3400912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6613839</t>
+          <t>6623987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6719803</t>
+          <t>6727496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1418-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75749</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78506</t>
+          <t>78519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116182</t>
+          <t>116492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>644089</t>
+          <t>643886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667452</t>
+          <t>667556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612602</t>
+          <t>612581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642497</t>
+          <t>641821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1266181</t>
+          <t>1265871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1303857</t>
+          <t>1303844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41060</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>70648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75244</t>
+          <t>75998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112277</t>
+          <t>114940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126297</t>
+          <t>126442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170850</t>
+          <t>174636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891517</t>
+          <t>891152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>920740</t>
+          <t>919934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>856116</t>
+          <t>853453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893149</t>
+          <t>892395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1759343</t>
+          <t>1755557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1803896</t>
+          <t>1803751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62403</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95553</t>
+          <t>96762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92663</t>
+          <t>93215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132520</t>
+          <t>136568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629209</t>
+          <t>629719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653351</t>
+          <t>653674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588288</t>
+          <t>587079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621438</t>
+          <t>620327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1229830</t>
+          <t>1225782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1269687</t>
+          <t>1269135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>66491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94191</t>
+          <t>95818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136114</t>
+          <t>136185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142156</t>
+          <t>143345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191085</t>
+          <t>191087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>875850</t>
+          <t>875731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902386</t>
+          <t>902032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>902498</t>
+          <t>902427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944421</t>
+          <t>942794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1789749</t>
+          <t>1789747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1838678</t>
+          <t>1837489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308880</t>
+          <t>309379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>381226</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>475182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>564282</t>
+          <t>565293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3069805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3122342</t>
+          <t>3120503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2997971</t>
+          <t>3000309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3070317</t>
+          <t>3069818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6091459</t>
+          <t>6090448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6173236</t>
+          <t>6180559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13143</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>31675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87753</t>
+          <t>87555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74530</t>
+          <t>72521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114026</t>
+          <t>111488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671061</t>
+          <t>671794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>690326</t>
+          <t>689580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609297</t>
+          <t>609495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>643361</t>
+          <t>643302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1286493</t>
+          <t>1289031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1325989</t>
+          <t>1327998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86086</t>
+          <t>86309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127342</t>
+          <t>125305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120126</t>
+          <t>120917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167173</t>
+          <t>169663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967321</t>
+          <t>967076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992050</t>
+          <t>991698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901631</t>
+          <t>903668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>942887</t>
+          <t>942664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1879748</t>
+          <t>1877258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1926795</t>
+          <t>1926004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>38026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>45115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76831</t>
+          <t>76251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>68031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105281</t>
+          <t>104778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719809</t>
+          <t>719597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742983</t>
+          <t>743895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>700343</t>
+          <t>700923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>730574</t>
+          <t>732059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1429516</t>
+          <t>1430019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1468644</t>
+          <t>1466766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90955</t>
+          <t>91998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131217</t>
+          <t>128966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114518</t>
+          <t>113269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159817</t>
+          <t>159354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911273</t>
+          <t>911651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932314</t>
+          <t>932687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919638</t>
+          <t>921889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959900</t>
+          <t>958857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1838777</t>
+          <t>1839240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884076</t>
+          <t>1885325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88191</t>
+          <t>86064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128787</t>
+          <t>129575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309986</t>
+          <t>312931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>383820</t>
+          <t>383193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413206</t>
+          <t>412841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494468</t>
+          <t>497025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3297992</t>
+          <t>3297204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3338588</t>
+          <t>3340715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3170232</t>
+          <t>3170859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3244066</t>
+          <t>3241121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6486363</t>
+          <t>6483806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6567625</t>
+          <t>6567990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60295</t>
+          <t>61059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>94755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641749</t>
+          <t>642164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659708</t>
+          <t>660220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>606362</t>
+          <t>605213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633941</t>
+          <t>635096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1254193</t>
+          <t>1252884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1287344</t>
+          <t>1286580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>36213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>49132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83337</t>
+          <t>81962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73156</t>
+          <t>72532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110060</t>
+          <t>110298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>986687</t>
+          <t>986218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006154</t>
+          <t>1006481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>959576</t>
+          <t>960951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992089</t>
+          <t>993781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1955284</t>
+          <t>1955046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1992188</t>
+          <t>1992812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76940</t>
+          <t>77408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98952</t>
+          <t>95961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>732336</t>
+          <t>731540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749302</t>
+          <t>749005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>708071</t>
+          <t>707603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>741017</t>
+          <t>739822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1445611</t>
+          <t>1448602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1485368</t>
+          <t>1485541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98270</t>
+          <t>94648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74809</t>
+          <t>73621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>910548</t>
+          <t>909945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927328</t>
+          <t>927363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945509</t>
+          <t>949131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984158</t>
+          <t>983420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867708</t>
+          <t>1868723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906537</t>
+          <t>1907725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223146</t>
+          <t>222423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289290</t>
+          <t>285859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>301375</t>
+          <t>294386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373029</t>
+          <t>373711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3294473</t>
+          <t>3292660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3330005</t>
+          <t>3329901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3255252</t>
+          <t>3258683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3321396</t>
+          <t>3322119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6565863</t>
+          <t>6565181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6637517</t>
+          <t>6644506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41935</t>
+          <t>44151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>57561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74673</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>93503</t>
+          <t>100217</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80243</t>
+          <t>84739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109060</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>605690</t>
+          <t>659576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593506</t>
+          <t>646559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613216</t>
+          <t>668425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>611317</t>
+          <t>663355</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600397</t>
+          <t>651357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620711</t>
+          <t>674876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1217008</t>
+          <t>1322930</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1201451</t>
+          <t>1307010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1230268</t>
+          <t>1338408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675070</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675070</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675070</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1423147</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1423147</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1423147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36779</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>55286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>89928</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94835</t>
+          <t>104260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118309</t>
+          <t>131126</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77495</t>
+          <t>113950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139685</t>
+          <t>151529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1154764</t>
+          <t>1006321</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1139398</t>
+          <t>992233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1172638</t>
+          <t>1015769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>873925</t>
+          <t>978126</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860621</t>
+          <t>963794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>885802</t>
+          <t>990979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2028690</t>
+          <t>1984447</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007314</t>
+          <t>1964044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2069504</t>
+          <t>2001623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>955456</t>
+          <t>1068054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>955456</t>
+          <t>1068054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>955456</t>
+          <t>1068054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2146999</t>
+          <t>2115573</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2146999</t>
+          <t>2115573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2146999</t>
+          <t>2115573</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>66226</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57951</t>
+          <t>85412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111680</t>
+          <t>121129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>670531</t>
+          <t>764522</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657075</t>
+          <t>750657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678782</t>
+          <t>774452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>873565</t>
+          <t>743004</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>849406</t>
+          <t>727883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>901150</t>
+          <t>755085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1544095</t>
+          <t>1507527</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521820</t>
+          <t>1488186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1575549</t>
+          <t>1523903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701821</t>
+          <t>800084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701821</t>
+          <t>800084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701821</t>
+          <t>800084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931679</t>
+          <t>809230</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931679</t>
+          <t>809230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931679</t>
+          <t>809230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633500</t>
+          <t>1609315</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633500</t>
+          <t>1609315</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633500</t>
+          <t>1609315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99283</t>
+          <t>103687</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78650</t>
+          <t>89375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121644</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>145357</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>125400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166703</t>
+          <t>166890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>884687</t>
+          <t>947297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867925</t>
+          <t>931745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>894851</t>
+          <t>957822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>991171</t>
+          <t>1012033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968810</t>
+          <t>994521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1011804</t>
+          <t>1026345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1875859</t>
+          <t>1959329</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1849526</t>
+          <t>1937796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897325</t>
+          <t>1979286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925775</t>
+          <t>988967</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925775</t>
+          <t>988967</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925775</t>
+          <t>988967</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090454</t>
+          <t>1115720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090454</t>
+          <t>1115720</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090454</t>
+          <t>1115720</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016229</t>
+          <t>2104686</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016229</t>
+          <t>2104686</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016229</t>
+          <t>2104686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109528</t>
+          <t>127983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163291</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251747</t>
+          <t>301096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340066</t>
+          <t>357002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379743</t>
+          <t>443396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>483252</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3315673</t>
+          <t>3377714</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3291289</t>
+          <t>3354893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3345052</t>
+          <t>3399296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3349979</t>
+          <t>3396518</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3312593</t>
+          <t>3368440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3400912</t>
+          <t>3424346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6665651</t>
+          <t>6774232</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6623987</t>
+          <t>6735595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6727496</t>
+          <t>6809325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
